--- a/nr-change-vs-address-disctrict/ig/CodeSystem-as-cs-intern-id-systems.xlsx
+++ b/nr-change-vs-address-disctrict/ig/CodeSystem-as-cs-intern-id-systems.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-06T17:38:45+00:00</t>
+    <t>2025-02-11T12:23:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
